--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2024_aysen.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2024_aysen.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:39</t>
+    <t xml:space="preserve">2026-10-05 01:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>827618.38</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>779052</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -800,7 +800,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>790092.12</v>
+        <v>790092.13</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>815571.81</v>
@@ -822,7 +822,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>876068.62</v>
+        <v>876068.63</v>
       </c>
       <c r="C13" s="2" t="n">
         <v>876986.31</v>
@@ -836,7 +836,7 @@
         <v>811102.38</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -899,7 +899,7 @@
         <v>21</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>814120.62</v>
+        <v>814120.63</v>
       </c>
       <c r="C20" s="2" t="n">
         <v>852706.38</v>
@@ -913,7 +913,7 @@
         <v>812580.06</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -921,7 +921,7 @@
         <v>23</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>870124.12</v>
+        <v>870124.13</v>
       </c>
       <c r="C22" s="2" t="n">
         <v>898176.25</v>
@@ -1001,7 +1001,7 @@
         <v>865382.19</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>870302.88</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1075,7 +1075,7 @@
         <v>37</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>876610.62</v>
+        <v>876610.63</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>900212.25</v>
@@ -1141,7 +1141,7 @@
         <v>43</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>906923.62</v>
+        <v>906923.63</v>
       </c>
       <c r="C42" s="2" t="n">
         <v>927625.75</v>
@@ -1152,7 +1152,7 @@
         <v>44</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>934345.62</v>
+        <v>934345.63</v>
       </c>
       <c r="C43" s="2" t="n">
         <v>943650.75</v>
@@ -1166,7 +1166,7 @@
         <v>923017.31</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1218,7 +1218,7 @@
         <v>50</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>1018368.62</v>
+        <v>1018368.63</v>
       </c>
       <c r="C49" s="2" t="n">
         <v>1049309.75</v>
@@ -1287,7 +1287,7 @@
         <v>1040954.38</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>1018930.31</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1339,10 +1339,10 @@
         <v>61</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1068712.12</v>
+        <v>1068712.13</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1350,7 +1350,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1149403.62</v>
+        <v>1149403.63</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>1183065.88</v>
@@ -1364,7 +1364,7 @@
         <v>1133819.25</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1419,7 +1419,7 @@
         <v>1179976</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1211880.62</v>
+        <v>1211880.63</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>1246393.5</v>
@@ -1504,7 +1504,7 @@
         <v>76</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1201814.12</v>
+        <v>1201814.13</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>1214165.25</v>
@@ -1518,7 +1518,7 @@
         <v>1242638.25</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1537,7 +1537,7 @@
         <v>79</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>1206327.12</v>
+        <v>1206327.13</v>
       </c>
       <c r="C78" s="2" t="n">
         <v>1242222.38</v>
@@ -1551,7 +1551,7 @@
         <v>1249670.5</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1231813.88</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1570,7 +1570,7 @@
         <v>82</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>1224898.62</v>
+        <v>1224898.63</v>
       </c>
       <c r="C81" s="2" t="n">
         <v>1271870.5</v>
@@ -1581,10 +1581,10 @@
         <v>83</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>1293449.12</v>
+        <v>1293449.13</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
@@ -1603,7 +1603,7 @@
         <v>85</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>1248465.12</v>
+        <v>1248465.13</v>
       </c>
       <c r="C84" s="2" t="n">
         <v>1282866.75</v>
